--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20240501_20241101.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20240501_20241101.xlsx
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
         <v>-17.46031746031747</v>
@@ -1124,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J16" t="n">
         <v>120.65</v>
@@ -1273,37 +1273,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>55.55555555555556</v>
+        <v>53.96825396825397</v>
       </c>
       <c r="C20" t="n">
-        <v>44.44444444444444</v>
+        <v>46.03174603174603</v>
       </c>
       <c r="D20" t="n">
-        <v>44.68758766962546</v>
+        <v>68.18788485029204</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>INE602A01031</t>
+          <t>INE205C01021</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>-11.11111111111111</v>
+        <v>-7.936507936507937</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="I20" t="n">
         <v>85</v>
       </c>
       <c r="J20" t="n">
-        <v>410.95</v>
+        <v>2874.3</v>
       </c>
       <c r="K20" t="n">
         <v>19</v>
@@ -1317,37 +1317,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53.96825396825397</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="C21" t="n">
-        <v>46.03174603174603</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="D21" t="n">
-        <v>68.18788485029204</v>
+        <v>44.68758766962546</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>INE205C01021</t>
+          <t>INE602A01031</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.936507936507937</v>
+        <v>-11.11111111111111</v>
       </c>
       <c r="H21" t="n">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="I21" t="n">
         <v>85</v>
       </c>
       <c r="J21" t="n">
-        <v>2874.3</v>
+        <v>410.95</v>
       </c>
       <c r="K21" t="n">
         <v>20</v>
